--- a/business-plan/収支計画_生活介護_広島市.xlsx
+++ b/business-plan/収支計画_生活介護_広島市.xlsx
@@ -14,6 +14,7 @@
     <sheet name="前提条件" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="人件費" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="収支計画5年" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="資金調達(会長借入)" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="137">
   <si>
     <r>
       <rPr>
@@ -2358,7 +2359,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">要有資格者</t>
+      <t xml:space="preserve">丸山氏が資格要件を満たしており確保済み</t>
     </r>
     <r>
       <rPr>
@@ -3401,6 +3402,416 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">会長への借入提案・返済シミュレーション</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">検討中のたたき台</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">青字セルが入力用です。借入額・据置期間・返済期間・金利を変更すると返済表が自動再計算されます。実際の条件は会長との相談のうえ決定してください。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">シナリオ</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：開設資金の一部</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(800</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">をお願いする場合</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">借入額</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">無担保想定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">据置期間</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">利息のみ支払い</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">据置後の元金均等返済期間</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">想定金利</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年率、仮</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">年目</t>
+  </si>
+  <si>
+    <t xml:space="preserve">期首残高</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元金返済</t>
+  </si>
+  <si>
+    <t xml:space="preserve">利息</t>
+  </si>
+  <si>
+    <t xml:space="preserve">年間支払</t>
+  </si>
+  <si>
+    <t xml:space="preserve">期末残高</t>
+  </si>
+  <si>
+    <t xml:space="preserve">返済総額</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">シナリオ</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：開設資金のほぼ全額</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(1,500</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">をお願いする場合</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※このシナリオでは、開設資金の残りは日本政策金融公庫の融資でまかなう想定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">シナリオ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。シナリオ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は開設資金のほぼ全額を会長借入でまかなう想定。実際の金利・返済期間・据置期間は会長との相談のうえ決定する。「収支計画</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年」シートの営業利益がマイナスの間は、この返済額を営業キャッシュフローだけで賄うのは厳しいため、据置期間の延長や返済額の見直しを早期に相談できる関係性を築いておくことが重要。</t>
     </r>
   </si>
 </sst>
@@ -4571,7 +4982,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
         <v>78</v>
       </c>
@@ -5343,4 +5754,530 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F34"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+    </row>
+    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B5" s="24" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B6" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B8" s="21" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="15" t="n">
+        <f aca="false">$B$5</f>
+        <v>8000000</v>
+      </c>
+      <c r="C11" s="15" t="n">
+        <f aca="false">IF(A11&lt;=$B$6,0,$B$5/$B$7)</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="15" t="n">
+        <f aca="false">B11*$B$8</f>
+        <v>160000</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <f aca="false">C11+D11</f>
+        <v>160000</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <f aca="false">B11-C11</f>
+        <v>8000000</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="15" t="n">
+        <f aca="false">F11</f>
+        <v>8000000</v>
+      </c>
+      <c r="C12" s="15" t="n">
+        <f aca="false">IF(A12&lt;=$B$6,0,$B$5/$B$7)</f>
+        <v>2000000</v>
+      </c>
+      <c r="D12" s="15" t="n">
+        <f aca="false">B12*$B$8</f>
+        <v>160000</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <f aca="false">C12+D12</f>
+        <v>2160000</v>
+      </c>
+      <c r="F12" s="15" t="n">
+        <f aca="false">B12-C12</f>
+        <v>6000000</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" s="15" t="n">
+        <f aca="false">F12</f>
+        <v>6000000</v>
+      </c>
+      <c r="C13" s="15" t="n">
+        <f aca="false">IF(A13&lt;=$B$6,0,$B$5/$B$7)</f>
+        <v>2000000</v>
+      </c>
+      <c r="D13" s="15" t="n">
+        <f aca="false">B13*$B$8</f>
+        <v>120000</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <f aca="false">C13+D13</f>
+        <v>2120000</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <f aca="false">B13-C13</f>
+        <v>4000000</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B14" s="15" t="n">
+        <f aca="false">F13</f>
+        <v>4000000</v>
+      </c>
+      <c r="C14" s="15" t="n">
+        <f aca="false">IF(A14&lt;=$B$6,0,$B$5/$B$7)</f>
+        <v>2000000</v>
+      </c>
+      <c r="D14" s="15" t="n">
+        <f aca="false">B14*$B$8</f>
+        <v>80000</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <f aca="false">C14+D14</f>
+        <v>2080000</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <f aca="false">B14-C14</f>
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B15" s="15" t="n">
+        <f aca="false">F14</f>
+        <v>2000000</v>
+      </c>
+      <c r="C15" s="15" t="n">
+        <f aca="false">IF(A15&lt;=$B$6,0,$B$5/$B$7)</f>
+        <v>2000000</v>
+      </c>
+      <c r="D15" s="15" t="n">
+        <f aca="false">B15*$B$8</f>
+        <v>40000</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <f aca="false">C15+D15</f>
+        <v>2040000</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <f aca="false">B15-C15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="13" t="n">
+        <f aca="false">SUM(D11:D15)</f>
+        <v>560000</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <f aca="false">SUM(E11:E15)</f>
+        <v>8560000</v>
+      </c>
+      <c r="F16" s="14"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B19" s="24" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B20" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B21" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B22" s="21" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B25" s="15" t="n">
+        <f aca="false">$B$19</f>
+        <v>15000000</v>
+      </c>
+      <c r="C25" s="15" t="n">
+        <f aca="false">IF(A25&lt;=$B$20,0,$B$19/$B$21)</f>
+        <v>0</v>
+      </c>
+      <c r="D25" s="15" t="n">
+        <f aca="false">B25*$B$22</f>
+        <v>300000</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <f aca="false">C25+D25</f>
+        <v>300000</v>
+      </c>
+      <c r="F25" s="15" t="n">
+        <f aca="false">B25-C25</f>
+        <v>15000000</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" s="15" t="n">
+        <f aca="false">F25</f>
+        <v>15000000</v>
+      </c>
+      <c r="C26" s="15" t="n">
+        <f aca="false">IF(A26&lt;=$B$20,0,$B$19/$B$21)</f>
+        <v>2500000</v>
+      </c>
+      <c r="D26" s="15" t="n">
+        <f aca="false">B26*$B$22</f>
+        <v>300000</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <f aca="false">C26+D26</f>
+        <v>2800000</v>
+      </c>
+      <c r="F26" s="15" t="n">
+        <f aca="false">B26-C26</f>
+        <v>12500000</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" s="15" t="n">
+        <f aca="false">F26</f>
+        <v>12500000</v>
+      </c>
+      <c r="C27" s="15" t="n">
+        <f aca="false">IF(A27&lt;=$B$20,0,$B$19/$B$21)</f>
+        <v>2500000</v>
+      </c>
+      <c r="D27" s="15" t="n">
+        <f aca="false">B27*$B$22</f>
+        <v>250000</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <f aca="false">C27+D27</f>
+        <v>2750000</v>
+      </c>
+      <c r="F27" s="15" t="n">
+        <f aca="false">B27-C27</f>
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B28" s="15" t="n">
+        <f aca="false">F27</f>
+        <v>10000000</v>
+      </c>
+      <c r="C28" s="15" t="n">
+        <f aca="false">IF(A28&lt;=$B$20,0,$B$19/$B$21)</f>
+        <v>2500000</v>
+      </c>
+      <c r="D28" s="15" t="n">
+        <f aca="false">B28*$B$22</f>
+        <v>200000</v>
+      </c>
+      <c r="E28" s="15" t="n">
+        <f aca="false">C28+D28</f>
+        <v>2700000</v>
+      </c>
+      <c r="F28" s="15" t="n">
+        <f aca="false">B28-C28</f>
+        <v>7500000</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B29" s="15" t="n">
+        <f aca="false">F28</f>
+        <v>7500000</v>
+      </c>
+      <c r="C29" s="15" t="n">
+        <f aca="false">IF(A29&lt;=$B$20,0,$B$19/$B$21)</f>
+        <v>2500000</v>
+      </c>
+      <c r="D29" s="15" t="n">
+        <f aca="false">B29*$B$22</f>
+        <v>150000</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <f aca="false">C29+D29</f>
+        <v>2650000</v>
+      </c>
+      <c r="F29" s="15" t="n">
+        <f aca="false">B29-C29</f>
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B30" s="15" t="n">
+        <f aca="false">F29</f>
+        <v>5000000</v>
+      </c>
+      <c r="C30" s="15" t="n">
+        <f aca="false">IF(A30&lt;=$B$20,0,$B$19/$B$21)</f>
+        <v>2500000</v>
+      </c>
+      <c r="D30" s="15" t="n">
+        <f aca="false">B30*$B$22</f>
+        <v>100000</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <f aca="false">C30+D30</f>
+        <v>2600000</v>
+      </c>
+      <c r="F30" s="15" t="n">
+        <f aca="false">B30-C30</f>
+        <v>2500000</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B31" s="15" t="n">
+        <f aca="false">F30</f>
+        <v>2500000</v>
+      </c>
+      <c r="C31" s="15" t="n">
+        <f aca="false">IF(A31&lt;=$B$20,0,$B$19/$B$21)</f>
+        <v>2500000</v>
+      </c>
+      <c r="D31" s="15" t="n">
+        <f aca="false">B31*$B$22</f>
+        <v>50000</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <f aca="false">C31+D31</f>
+        <v>2550000</v>
+      </c>
+      <c r="F31" s="15" t="n">
+        <f aca="false">B31-C31</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="13" t="n">
+        <f aca="false">SUM(D25:D31)</f>
+        <v>1350000</v>
+      </c>
+      <c r="E32" s="13" t="n">
+        <f aca="false">SUM(E25:E31)</f>
+        <v>16350000</v>
+      </c>
+      <c r="F32" s="14"/>
+    </row>
+    <row r="34" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A34:F34"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/business-plan/収支計画_生活介護_広島市.xlsx
+++ b/business-plan/収支計画_生活介護_広島市.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="231">
   <si>
     <r>
       <rPr>
@@ -1098,7 +1098,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">㎡超で必須</t>
+      <t xml:space="preserve">㎡超は原則必要。ただし類似用途間の転用は不要となる余地あり</t>
     </r>
     <r>
       <rPr>
@@ -1155,7 +1155,121 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">ため、控除対象外消費税を別行で計上。金額は全て税込の概算。</t>
+      <t xml:space="preserve">ため、下記の物件取得費〜予備費は本体価格</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">税抜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で計上し、消費税は別行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">控除対象外消費税</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">でまとめて加算する</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">税込金額に重ねて課税しないよう、二重計上に注意</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。</t>
     </r>
   </si>
   <si>
@@ -1191,7 +1305,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">税込</t>
+      <t xml:space="preserve">税抜</t>
     </r>
     <r>
       <rPr>
@@ -3246,36 +3360,17 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">生活介護の人件費割合</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(45%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">と仮定</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)=</t>
+      <t xml:space="preserve">通所系サービスの人件費割合</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(55%)=</t>
     </r>
     <r>
       <rPr>
@@ -3294,16 +3389,92 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">4.5%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">上乗せの概算値。正式な地域区分・人件費割合は広島市提示の単価表で必ず確認。</t>
+      <t xml:space="preserve">5.5%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">上乗せの概算値</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改訂前は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">45%=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">施設系の割合を誤用していたため</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">55%=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">通所系に是正</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。正式な地域区分・人件費割合は広島市提示の単価表で必ず確認。</t>
     </r>
   </si>
   <si>
@@ -6465,7 +6636,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">居抜き物件の徹底活用で内装費を圧縮 ②内装・什器の仕様グレードダウン ③自己資金の積み増し</t>
+      <t xml:space="preserve">収支計画</t>
     </r>
     <r>
       <rPr>
@@ -6475,6 +6646,25 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年シートの人員配置</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">(</t>
     </r>
     <r>
@@ -6484,6 +6674,82 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">生活支援員等の人数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を法定最低ラインに近づけ、取り漏れている加算</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人員配置体制加算等</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を反映して収支そのものを改善する ②居抜き物件の徹底活用で内装費を圧縮 ③内装・什器の仕様グレードダウン ④自己資金の積み増し</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">自己資金比率は融資審査にも直結</t>
     </r>
     <r>
@@ -6494,16 +6760,16 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">) ④</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">会長借入の増額交渉 ⑤地方銀行・信用金庫の制度融資の追加活用 ⑥定員</t>
+      <t xml:space="preserve">) ⑤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">会長借入の増額交渉 ⑥地方銀行・信用金庫の制度融資の追加活用 ⑦多機能型化</t>
     </r>
     <r>
       <rPr>
@@ -6513,16 +6779,16 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">18</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">名等での小さく開所し、稼働率が安定した段階で定員変更</t>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">生活介護単独の最低定員</t>
     </r>
     <r>
       <rPr>
@@ -6532,17 +6798,259 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名は変更不可のため、定員縮小ではなく他事業との組み合わせで固定費を分散する</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ヵ年累積を踏まえた真の必要資金・ギャップ】</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">増員</t>
-    </r>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">重要</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">設備投資等</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">初期投資合計－運転資金</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ヵ年累積キャッシュフロー不足</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">収支計画</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年シート</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Year5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">真の必要資金総額</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">真の資金ギャップ</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">調達合計－真の必要資金総額</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -6551,16 +7059,111 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を申請する段階的展開も選択肢</t>
+      <t xml:space="preserve">Year1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の運転資金のみを基準にした「過不足」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">上記</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は約▲</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2,400</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円台だったが、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Year2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以降も営業赤字・現金流出が続くため、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ヵ年累積で見た真のギャップはこれより大幅に大きい。資金調達・会長への提案は、この「真の資金ギャップ」を基準に検討すること。</t>
     </r>
   </si>
   <si>
@@ -9310,7 +9913,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -9433,6 +10036,10 @@
     </xf>
     <xf numFmtId="165" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
@@ -10058,7 +10665,7 @@
       </c>
       <c r="B14" s="13" t="n">
         <f aca="false">-'月次資金繰り(Year1)'!$B$17</f>
-        <v>33367211.40672</v>
+        <v>33208026.82688</v>
       </c>
       <c r="C14" s="14"/>
       <c r="D14" s="12" t="s">
@@ -10071,7 +10678,7 @@
       </c>
       <c r="B15" s="16" t="n">
         <f aca="false">SUM(B4:B14)</f>
-        <v>64017211.40672</v>
+        <v>63858026.82688</v>
       </c>
       <c r="C15" s="17"/>
       <c r="D15" s="17"/>
@@ -10208,7 +10815,7 @@
         <v>64</v>
       </c>
       <c r="B9" s="20" t="n">
-        <v>10.45</v>
+        <v>10.55</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>65</v>
@@ -10717,7 +11324,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
@@ -10750,7 +11357,7 @@
       </c>
       <c r="B5" s="28" t="n">
         <f aca="false">初期投資!$B$15</f>
-        <v>64017211.40672</v>
+        <v>63858026.82688</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10829,7 +11436,7 @@
       </c>
       <c r="B14" s="30" t="n">
         <f aca="false">B13-B5</f>
-        <v>-24017211.40672</v>
+        <v>-23858026.82688</v>
       </c>
       <c r="C14" s="14"/>
     </row>
@@ -10840,11 +11447,60 @@
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
     </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="B18" s="13" t="n">
+        <f aca="false">B5-初期投資!$B$14</f>
+        <v>30650000</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="B19" s="13" t="n">
+        <f aca="false">-収支計画5年!$F$33</f>
+        <v>79462700</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="B20" s="16" t="n">
+        <f aca="false">B18+B19</f>
+        <v>110112700</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="B21" s="30" t="n">
+        <f aca="false">B13-B20</f>
+        <v>-70112700</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="B22" s="31"/>
+      <c r="C22" s="31"/>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A22:C22"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -10870,7 +11526,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -10879,7 +11535,7 @@
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -10888,12 +11544,12 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B5" s="24" t="n">
         <v>10000000</v>
@@ -10904,55 +11560,55 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="B6" s="18" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B7" s="18" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B8" s="23" t="n">
         <v>0.03</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11107,7 +11763,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B17" s="17"/>
       <c r="C17" s="17"/>
@@ -11123,12 +11779,12 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B20" s="24" t="n">
         <v>15000000</v>
@@ -11139,55 +11795,55 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="B21" s="18" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B22" s="18" t="n">
         <v>6</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B23" s="23" t="n">
         <v>0.035</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11367,7 +12023,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B33" s="17"/>
       <c r="C33" s="17"/>
@@ -11383,7 +12039,7 @@
     </row>
     <row r="35" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
@@ -11421,7 +12077,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -11439,7 +12095,7 @@
     </row>
     <row r="2" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -11460,45 +12116,45 @@
         <v>14</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B5" s="19" t="n">
         <v>3</v>
@@ -11539,7 +12195,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B6" s="21" t="n">
         <v>0.8</v>
@@ -11580,7 +12236,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B7" s="18" t="n">
         <v>21</v>
@@ -11621,219 +12277,219 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="B8" s="31" t="n">
+        <v>188</v>
+      </c>
+      <c r="B8" s="32" t="n">
         <f aca="false">B5*B6</f>
         <v>2.4</v>
       </c>
-      <c r="C8" s="31" t="n">
+      <c r="C8" s="32" t="n">
         <f aca="false">C5*C6</f>
         <v>4</v>
       </c>
-      <c r="D8" s="31" t="n">
+      <c r="D8" s="32" t="n">
         <f aca="false">D5*D6</f>
         <v>5.6</v>
       </c>
-      <c r="E8" s="31" t="n">
+      <c r="E8" s="32" t="n">
         <f aca="false">E5*E6</f>
         <v>7.2</v>
       </c>
-      <c r="F8" s="31" t="n">
+      <c r="F8" s="32" t="n">
         <f aca="false">F5*F6</f>
         <v>8</v>
       </c>
-      <c r="G8" s="31" t="n">
+      <c r="G8" s="32" t="n">
         <f aca="false">G5*G6</f>
         <v>8.8</v>
       </c>
-      <c r="H8" s="31" t="n">
+      <c r="H8" s="32" t="n">
         <f aca="false">H5*H6</f>
         <v>9.6</v>
       </c>
-      <c r="I8" s="31" t="n">
+      <c r="I8" s="32" t="n">
         <f aca="false">I5*I6</f>
         <v>10.4</v>
       </c>
-      <c r="J8" s="31" t="n">
+      <c r="J8" s="32" t="n">
         <f aca="false">J5*J6</f>
         <v>10.4</v>
       </c>
-      <c r="K8" s="31" t="n">
+      <c r="K8" s="32" t="n">
         <f aca="false">K5*K6</f>
         <v>11.2</v>
       </c>
-      <c r="L8" s="31" t="n">
+      <c r="L8" s="32" t="n">
         <f aca="false">L5*L6</f>
         <v>11.2</v>
       </c>
-      <c r="M8" s="31" t="n">
+      <c r="M8" s="32" t="n">
         <f aca="false">M5*M6</f>
         <v>12</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="B9" s="32" t="n">
+        <v>189</v>
+      </c>
+      <c r="B9" s="33" t="n">
         <f aca="false">B8/前提条件!$B$3</f>
         <v>0.12</v>
       </c>
-      <c r="C9" s="32" t="n">
+      <c r="C9" s="33" t="n">
         <f aca="false">C8/前提条件!$B$3</f>
         <v>0.2</v>
       </c>
-      <c r="D9" s="32" t="n">
+      <c r="D9" s="33" t="n">
         <f aca="false">D8/前提条件!$B$3</f>
         <v>0.28</v>
       </c>
-      <c r="E9" s="32" t="n">
+      <c r="E9" s="33" t="n">
         <f aca="false">E8/前提条件!$B$3</f>
         <v>0.36</v>
       </c>
-      <c r="F9" s="32" t="n">
+      <c r="F9" s="33" t="n">
         <f aca="false">F8/前提条件!$B$3</f>
         <v>0.4</v>
       </c>
-      <c r="G9" s="32" t="n">
+      <c r="G9" s="33" t="n">
         <f aca="false">G8/前提条件!$B$3</f>
         <v>0.44</v>
       </c>
-      <c r="H9" s="32" t="n">
+      <c r="H9" s="33" t="n">
         <f aca="false">H8/前提条件!$B$3</f>
         <v>0.48</v>
       </c>
-      <c r="I9" s="32" t="n">
+      <c r="I9" s="33" t="n">
         <f aca="false">I8/前提条件!$B$3</f>
         <v>0.52</v>
       </c>
-      <c r="J9" s="32" t="n">
+      <c r="J9" s="33" t="n">
         <f aca="false">J8/前提条件!$B$3</f>
         <v>0.52</v>
       </c>
-      <c r="K9" s="32" t="n">
+      <c r="K9" s="33" t="n">
         <f aca="false">K8/前提条件!$B$3</f>
         <v>0.56</v>
       </c>
-      <c r="L9" s="32" t="n">
+      <c r="L9" s="33" t="n">
         <f aca="false">L8/前提条件!$B$3</f>
         <v>0.56</v>
       </c>
-      <c r="M9" s="32" t="n">
+      <c r="M9" s="33" t="n">
         <f aca="false">M8/前提条件!$B$3</f>
         <v>0.6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="B10" s="13" t="n">
         <f aca="false">前提条件!$B$5*前提条件!$B$9+前提条件!$B$13*(前提条件!$B$10+前提条件!$B$12*前提条件!$B$11)*前提条件!$B$9+前提条件!$B$5*前提条件!$B$9*前提条件!$B$14</f>
-        <v>10926.6872</v>
+        <v>11031.2488</v>
       </c>
       <c r="C10" s="13" t="n">
         <f aca="false">前提条件!$B$5*前提条件!$B$9+前提条件!$B$13*(前提条件!$B$10+前提条件!$B$12*前提条件!$B$11)*前提条件!$B$9+前提条件!$B$5*前提条件!$B$9*前提条件!$B$14</f>
-        <v>10926.6872</v>
+        <v>11031.2488</v>
       </c>
       <c r="D10" s="13" t="n">
         <f aca="false">前提条件!$B$5*前提条件!$B$9+前提条件!$B$13*(前提条件!$B$10+前提条件!$B$12*前提条件!$B$11)*前提条件!$B$9+前提条件!$B$5*前提条件!$B$9*前提条件!$B$14</f>
-        <v>10926.6872</v>
+        <v>11031.2488</v>
       </c>
       <c r="E10" s="13" t="n">
         <f aca="false">前提条件!$B$5*前提条件!$B$9+前提条件!$B$13*(前提条件!$B$10+前提条件!$B$12*前提条件!$B$11)*前提条件!$B$9+前提条件!$B$5*前提条件!$B$9*前提条件!$B$14</f>
-        <v>10926.6872</v>
+        <v>11031.2488</v>
       </c>
       <c r="F10" s="13" t="n">
         <f aca="false">前提条件!$B$5*前提条件!$B$9+前提条件!$B$13*(前提条件!$B$10+前提条件!$B$12*前提条件!$B$11)*前提条件!$B$9+前提条件!$B$5*前提条件!$B$9*前提条件!$B$14</f>
-        <v>10926.6872</v>
+        <v>11031.2488</v>
       </c>
       <c r="G10" s="13" t="n">
         <f aca="false">前提条件!$B$5*前提条件!$B$9+前提条件!$B$13*(前提条件!$B$10+前提条件!$B$12*前提条件!$B$11)*前提条件!$B$9+前提条件!$B$5*前提条件!$B$9*前提条件!$B$14</f>
-        <v>10926.6872</v>
+        <v>11031.2488</v>
       </c>
       <c r="H10" s="13" t="n">
         <f aca="false">前提条件!$B$5*前提条件!$B$9+前提条件!$B$13*(前提条件!$B$10+前提条件!$B$12*前提条件!$B$11)*前提条件!$B$9+前提条件!$B$5*前提条件!$B$9*前提条件!$B$14</f>
-        <v>10926.6872</v>
+        <v>11031.2488</v>
       </c>
       <c r="I10" s="13" t="n">
         <f aca="false">前提条件!$B$5*前提条件!$B$9+前提条件!$B$13*(前提条件!$B$10+前提条件!$B$12*前提条件!$B$11)*前提条件!$B$9+前提条件!$B$5*前提条件!$B$9*前提条件!$B$14</f>
-        <v>10926.6872</v>
+        <v>11031.2488</v>
       </c>
       <c r="J10" s="13" t="n">
         <f aca="false">前提条件!$B$5*前提条件!$B$9+前提条件!$B$13*(前提条件!$B$10+前提条件!$B$12*前提条件!$B$11)*前提条件!$B$9+前提条件!$B$5*前提条件!$B$9*前提条件!$B$14</f>
-        <v>10926.6872</v>
+        <v>11031.2488</v>
       </c>
       <c r="K10" s="13" t="n">
         <f aca="false">前提条件!$B$5*前提条件!$B$9+前提条件!$B$13*(前提条件!$B$10+前提条件!$B$12*前提条件!$B$11)*前提条件!$B$9+前提条件!$B$5*前提条件!$B$9*前提条件!$B$14</f>
-        <v>10926.6872</v>
+        <v>11031.2488</v>
       </c>
       <c r="L10" s="13" t="n">
         <f aca="false">前提条件!$B$5*前提条件!$B$9+前提条件!$B$13*(前提条件!$B$10+前提条件!$B$12*前提条件!$B$11)*前提条件!$B$9+前提条件!$B$5*前提条件!$B$9*前提条件!$B$14</f>
-        <v>10926.6872</v>
+        <v>11031.2488</v>
       </c>
       <c r="M10" s="13" t="n">
         <f aca="false">前提条件!$B$5*前提条件!$B$9+前提条件!$B$13*(前提条件!$B$10+前提条件!$B$12*前提条件!$B$11)*前提条件!$B$9+前提条件!$B$5*前提条件!$B$9*前提条件!$B$14</f>
-        <v>10926.6872</v>
+        <v>11031.2488</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B11" s="13" t="n">
         <f aca="false">B8*B10*B7</f>
-        <v>550705.03488</v>
+        <v>555974.93952</v>
       </c>
       <c r="C11" s="13" t="n">
         <f aca="false">C8*C10*C7</f>
-        <v>917841.7248</v>
+        <v>926624.8992</v>
       </c>
       <c r="D11" s="13" t="n">
         <f aca="false">D8*D10*D7</f>
-        <v>1284978.41472</v>
+        <v>1297274.85888</v>
       </c>
       <c r="E11" s="13" t="n">
         <f aca="false">E8*E10*E7</f>
-        <v>1652115.10464</v>
+        <v>1667924.81856</v>
       </c>
       <c r="F11" s="13" t="n">
         <f aca="false">F8*F10*F7</f>
-        <v>1835683.4496</v>
+        <v>1853249.7984</v>
       </c>
       <c r="G11" s="13" t="n">
         <f aca="false">G8*G10*G7</f>
-        <v>2019251.79456</v>
+        <v>2038574.77824</v>
       </c>
       <c r="H11" s="13" t="n">
         <f aca="false">H8*H10*H7</f>
-        <v>2202820.13952</v>
+        <v>2223899.75808</v>
       </c>
       <c r="I11" s="13" t="n">
         <f aca="false">I8*I10*I7</f>
-        <v>2386388.48448</v>
+        <v>2409224.73792</v>
       </c>
       <c r="J11" s="13" t="n">
         <f aca="false">J8*J10*J7</f>
-        <v>1704563.2032</v>
+        <v>1720874.8128</v>
       </c>
       <c r="K11" s="13" t="n">
         <f aca="false">K8*K10*K7</f>
-        <v>2080441.24288</v>
+        <v>2100349.77152</v>
       </c>
       <c r="L11" s="13" t="n">
         <f aca="false">L8*L10*L7</f>
-        <v>2569956.82944</v>
+        <v>2594549.71776</v>
       </c>
       <c r="M11" s="13" t="n">
         <f aca="false">M8*M10*M7</f>
-        <v>2753525.1744</v>
+        <v>2779874.6976</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="B12" s="13" t="n">
         <v>0</v>
@@ -11843,48 +12499,48 @@
       </c>
       <c r="D12" s="13" t="n">
         <f aca="false">B11</f>
-        <v>550705.03488</v>
+        <v>555974.93952</v>
       </c>
       <c r="E12" s="13" t="n">
         <f aca="false">C11</f>
-        <v>917841.7248</v>
+        <v>926624.8992</v>
       </c>
       <c r="F12" s="13" t="n">
         <f aca="false">D11</f>
-        <v>1284978.41472</v>
+        <v>1297274.85888</v>
       </c>
       <c r="G12" s="13" t="n">
         <f aca="false">E11</f>
-        <v>1652115.10464</v>
+        <v>1667924.81856</v>
       </c>
       <c r="H12" s="13" t="n">
         <f aca="false">F11</f>
-        <v>1835683.4496</v>
+        <v>1853249.7984</v>
       </c>
       <c r="I12" s="13" t="n">
         <f aca="false">G11</f>
-        <v>2019251.79456</v>
+        <v>2038574.77824</v>
       </c>
       <c r="J12" s="13" t="n">
         <f aca="false">H11</f>
-        <v>2202820.13952</v>
+        <v>2223899.75808</v>
       </c>
       <c r="K12" s="13" t="n">
         <f aca="false">I11</f>
-        <v>2386388.48448</v>
+        <v>2409224.73792</v>
       </c>
       <c r="L12" s="13" t="n">
         <f aca="false">J11</f>
-        <v>1704563.2032</v>
+        <v>1720874.8128</v>
       </c>
       <c r="M12" s="13" t="n">
         <f aca="false">K11</f>
-        <v>2080441.24288</v>
+        <v>2100349.77152</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B13" s="13" t="n">
         <f aca="false">人件費!$D$12/12+前提条件!$B$21+前提条件!$B$23/12+前提条件!$B$22/12</f>
@@ -11937,7 +12593,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="29" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B14" s="16" t="n">
         <f aca="false">B12-B13</f>
@@ -11949,48 +12605,48 @@
       </c>
       <c r="D14" s="16" t="n">
         <f aca="false">D12-D13</f>
-        <v>-3616128.29845333</v>
+        <v>-3610858.39381333</v>
       </c>
       <c r="E14" s="16" t="n">
         <f aca="false">E12-E13</f>
-        <v>-3248991.60853333</v>
+        <v>-3240208.43413333</v>
       </c>
       <c r="F14" s="16" t="n">
         <f aca="false">F12-F13</f>
-        <v>-2881854.91861333</v>
+        <v>-2869558.47445333</v>
       </c>
       <c r="G14" s="16" t="n">
         <f aca="false">G12-G13</f>
-        <v>-2514718.22869333</v>
+        <v>-2498908.51477333</v>
       </c>
       <c r="H14" s="16" t="n">
         <f aca="false">H12-H13</f>
-        <v>-2331149.88373333</v>
+        <v>-2313583.53493333</v>
       </c>
       <c r="I14" s="16" t="n">
         <f aca="false">I12-I13</f>
-        <v>-2147581.53877333</v>
+        <v>-2128258.55509333</v>
       </c>
       <c r="J14" s="16" t="n">
         <f aca="false">J12-J13</f>
-        <v>-1964013.19381333</v>
+        <v>-1942933.57525333</v>
       </c>
       <c r="K14" s="16" t="n">
         <f aca="false">K12-K13</f>
-        <v>-1780444.84885333</v>
+        <v>-1757608.59541333</v>
       </c>
       <c r="L14" s="16" t="n">
         <f aca="false">L12-L13</f>
-        <v>-2462270.13013333</v>
+        <v>-2445958.52053333</v>
       </c>
       <c r="M14" s="16" t="n">
         <f aca="false">M12-M13</f>
-        <v>-2086392.09045333</v>
+        <v>-2066483.56181333</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="29" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B15" s="30" t="n">
         <f aca="false">B14</f>
@@ -12002,43 +12658,43 @@
       </c>
       <c r="D15" s="30" t="n">
         <f aca="false">C15+D14</f>
-        <v>-11949794.96512</v>
+        <v>-11944525.06048</v>
       </c>
       <c r="E15" s="30" t="n">
         <f aca="false">D15+E14</f>
-        <v>-15198786.5736533</v>
+        <v>-15184733.4946133</v>
       </c>
       <c r="F15" s="30" t="n">
         <f aca="false">E15+F14</f>
-        <v>-18080641.4922667</v>
+        <v>-18054291.9690667</v>
       </c>
       <c r="G15" s="30" t="n">
         <f aca="false">F15+G14</f>
-        <v>-20595359.72096</v>
+        <v>-20553200.48384</v>
       </c>
       <c r="H15" s="30" t="n">
         <f aca="false">G15+H14</f>
-        <v>-22926509.6046933</v>
+        <v>-22866784.0187733</v>
       </c>
       <c r="I15" s="30" t="n">
         <f aca="false">H15+I14</f>
-        <v>-25074091.1434667</v>
+        <v>-24995042.5738667</v>
       </c>
       <c r="J15" s="30" t="n">
         <f aca="false">I15+J14</f>
-        <v>-27038104.33728</v>
+        <v>-26937976.14912</v>
       </c>
       <c r="K15" s="30" t="n">
         <f aca="false">J15+K14</f>
-        <v>-28818549.1861333</v>
+        <v>-28695584.7445333</v>
       </c>
       <c r="L15" s="30" t="n">
         <f aca="false">K15+L14</f>
-        <v>-31280819.3162667</v>
+        <v>-31141543.2650667</v>
       </c>
       <c r="M15" s="30" t="n">
         <f aca="false">L15+M14</f>
-        <v>-33367211.40672</v>
+        <v>-33208026.82688</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12058,14 +12714,14 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="B17" s="33" t="n">
+        <v>196</v>
+      </c>
+      <c r="B17" s="34" t="n">
         <f aca="false">MIN(B15:M15)</f>
-        <v>-33367211.40672</v>
+        <v>-33208026.82688</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
@@ -12108,38 +12764,38 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="34" t="s">
-        <v>192</v>
-      </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
+      <c r="A1" s="35" t="s">
+        <v>198</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="35" t="s">
-        <v>193</v>
-      </c>
-      <c r="C2" s="35" t="s">
-        <v>194</v>
-      </c>
-      <c r="D2" s="35" t="s">
-        <v>195</v>
-      </c>
-      <c r="E2" s="35" t="s">
-        <v>196</v>
-      </c>
-      <c r="F2" s="35" t="s">
-        <v>197</v>
+      <c r="B2" s="36" t="s">
+        <v>199</v>
+      </c>
+      <c r="C2" s="36" t="s">
+        <v>200</v>
+      </c>
+      <c r="D2" s="36" t="s">
+        <v>201</v>
+      </c>
+      <c r="E2" s="36" t="s">
+        <v>202</v>
+      </c>
+      <c r="F2" s="36" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B3" s="23" t="n">
         <v>0.35</v>
@@ -12159,77 +12815,77 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="B4" s="31" t="n">
+        <v>205</v>
+      </c>
+      <c r="B4" s="32" t="n">
         <f aca="false">前提条件!$B$3*B3</f>
         <v>7</v>
       </c>
-      <c r="C4" s="31" t="n">
+      <c r="C4" s="32" t="n">
         <f aca="false">前提条件!$B$3*C3</f>
         <v>13</v>
       </c>
-      <c r="D4" s="31" t="n">
+      <c r="D4" s="32" t="n">
         <f aca="false">前提条件!$B$3*D3</f>
         <v>16</v>
       </c>
-      <c r="E4" s="31" t="n">
+      <c r="E4" s="32" t="n">
         <f aca="false">前提条件!$B$3*E3</f>
         <v>17</v>
       </c>
-      <c r="F4" s="31" t="n">
+      <c r="F4" s="32" t="n">
         <f aca="false">前提条件!$B$3*F3</f>
         <v>17</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="B5" s="36" t="n">
+        <v>206</v>
+      </c>
+      <c r="B5" s="37" t="n">
         <f aca="false">前提条件!$B$20</f>
         <v>250</v>
       </c>
-      <c r="C5" s="36" t="n">
+      <c r="C5" s="37" t="n">
         <f aca="false">前提条件!$B$20</f>
         <v>250</v>
       </c>
-      <c r="D5" s="36" t="n">
+      <c r="D5" s="37" t="n">
         <f aca="false">前提条件!$B$20</f>
         <v>250</v>
       </c>
-      <c r="E5" s="36" t="n">
+      <c r="E5" s="37" t="n">
         <f aca="false">前提条件!$B$20</f>
         <v>250</v>
       </c>
-      <c r="F5" s="36" t="n">
+      <c r="F5" s="37" t="n">
         <f aca="false">前提条件!$B$20</f>
         <v>250</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B6" s="13" t="n">
         <f aca="false">前提条件!$B$5*前提条件!$B$9</f>
-        <v>10073.8</v>
+        <v>10170.2</v>
       </c>
       <c r="C6" s="13" t="n">
         <f aca="false">前提条件!$B$5*前提条件!$B$9</f>
-        <v>10073.8</v>
+        <v>10170.2</v>
       </c>
       <c r="D6" s="13" t="n">
         <f aca="false">前提条件!$B$5*前提条件!$B$9</f>
-        <v>10073.8</v>
+        <v>10170.2</v>
       </c>
       <c r="E6" s="13" t="n">
         <f aca="false">前提条件!$B$5*前提条件!$B$9</f>
-        <v>10073.8</v>
+        <v>10170.2</v>
       </c>
       <c r="F6" s="13" t="n">
         <f aca="false">前提条件!$B$5*前提条件!$B$9</f>
-        <v>10073.8</v>
+        <v>10170.2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12242,7 +12898,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="29" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
@@ -12252,152 +12908,152 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B9" s="13" t="n">
         <f aca="false">B4*B6*B5</f>
-        <v>17629150</v>
+        <v>17797850</v>
       </c>
       <c r="C9" s="13" t="n">
         <f aca="false">C4*C6*C5</f>
-        <v>32739850</v>
+        <v>33053150</v>
       </c>
       <c r="D9" s="13" t="n">
         <f aca="false">D4*D6*D5</f>
-        <v>40295200</v>
+        <v>40680800</v>
       </c>
       <c r="E9" s="13" t="n">
         <f aca="false">E4*E6*E5</f>
-        <v>42813650</v>
+        <v>43223350</v>
       </c>
       <c r="F9" s="13" t="n">
         <f aca="false">F4*F6*F5</f>
-        <v>42813650</v>
+        <v>43223350</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="B10" s="13" t="n">
         <f aca="false">B4*前提条件!$B$13*((前提条件!$B$10+前提条件!$B$12*前提条件!$B$11)*2)*前提条件!$B$9*B5</f>
-        <v>1433740</v>
+        <v>1447460</v>
       </c>
       <c r="C10" s="13" t="n">
         <f aca="false">C4*前提条件!$B$13*((前提条件!$B$10+前提条件!$B$12*前提条件!$B$11)*2)*前提条件!$B$9*C5</f>
-        <v>2662660</v>
+        <v>2688140</v>
       </c>
       <c r="D10" s="13" t="n">
         <f aca="false">D4*前提条件!$B$13*((前提条件!$B$10+前提条件!$B$12*前提条件!$B$11)*2)*前提条件!$B$9*D5</f>
-        <v>3277120</v>
+        <v>3308480</v>
       </c>
       <c r="E10" s="13" t="n">
         <f aca="false">E4*前提条件!$B$13*((前提条件!$B$10+前提条件!$B$12*前提条件!$B$11)*2)*前提条件!$B$9*E5</f>
-        <v>3481940</v>
+        <v>3515260</v>
       </c>
       <c r="F10" s="13" t="n">
         <f aca="false">F4*前提条件!$B$13*((前提条件!$B$10+前提条件!$B$12*前提条件!$B$11)*2)*前提条件!$B$9*F5</f>
-        <v>3481940</v>
+        <v>3515260</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B11" s="13" t="n">
         <f aca="false">B9*前提条件!$B$14</f>
-        <v>775682.6</v>
+        <v>783105.4</v>
       </c>
       <c r="C11" s="13" t="n">
         <f aca="false">C9*前提条件!$B$14</f>
-        <v>1440553.4</v>
+        <v>1454338.6</v>
       </c>
       <c r="D11" s="13" t="n">
         <f aca="false">D9*前提条件!$B$14</f>
-        <v>1772988.8</v>
+        <v>1789955.2</v>
       </c>
       <c r="E11" s="13" t="n">
         <f aca="false">E9*前提条件!$B$14</f>
-        <v>1883800.6</v>
+        <v>1901827.4</v>
       </c>
       <c r="F11" s="13" t="n">
         <f aca="false">F9*前提条件!$B$14</f>
-        <v>1883800.6</v>
+        <v>1901827.4</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B12" s="13" t="n">
         <f aca="false">B4*前提条件!$B$15*前提条件!$B$16*(前提条件!$B$20/5)*前提条件!$B$17*前提条件!$B$9</f>
-        <v>146300</v>
+        <v>147700</v>
       </c>
       <c r="C12" s="13" t="n">
         <f aca="false">C4*前提条件!$B$15*前提条件!$B$16*(前提条件!$B$20/5)*前提条件!$B$17*前提条件!$B$9</f>
-        <v>271700</v>
+        <v>274300</v>
       </c>
       <c r="D12" s="13" t="n">
         <f aca="false">D4*前提条件!$B$15*前提条件!$B$16*(前提条件!$B$20/5)*前提条件!$B$17*前提条件!$B$9</f>
-        <v>334400</v>
+        <v>337600</v>
       </c>
       <c r="E12" s="13" t="n">
         <f aca="false">E4*前提条件!$B$15*前提条件!$B$16*(前提条件!$B$20/5)*前提条件!$B$17*前提条件!$B$9</f>
-        <v>355300</v>
+        <v>358700</v>
       </c>
       <c r="F12" s="13" t="n">
         <f aca="false">F4*前提条件!$B$15*前提条件!$B$16*(前提条件!$B$20/5)*前提条件!$B$17*前提条件!$B$9</f>
-        <v>355300</v>
+        <v>358700</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B13" s="13" t="n">
         <f aca="false">B4*前提条件!$B$18*前提条件!$B$19*前提条件!$B$9*B5</f>
-        <v>526680</v>
+        <v>531720</v>
       </c>
       <c r="C13" s="13" t="n">
         <f aca="false">C4*前提条件!$B$18*前提条件!$B$19*前提条件!$B$9*C5</f>
-        <v>978120</v>
+        <v>987480</v>
       </c>
       <c r="D13" s="13" t="n">
         <f aca="false">D4*前提条件!$B$18*前提条件!$B$19*前提条件!$B$9*D5</f>
-        <v>1203840</v>
+        <v>1215360</v>
       </c>
       <c r="E13" s="13" t="n">
         <f aca="false">E4*前提条件!$B$18*前提条件!$B$19*前提条件!$B$9*E5</f>
-        <v>1279080</v>
+        <v>1291320</v>
       </c>
       <c r="F13" s="13" t="n">
         <f aca="false">F4*前提条件!$B$18*前提条件!$B$19*前提条件!$B$9*F5</f>
-        <v>1279080</v>
+        <v>1291320</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="29" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B14" s="16" t="n">
         <f aca="false">SUM(B9:B13)</f>
-        <v>20511552.6</v>
+        <v>20707835.4</v>
       </c>
       <c r="C14" s="16" t="n">
         <f aca="false">SUM(C9:C13)</f>
-        <v>38092883.4</v>
+        <v>38457408.6</v>
       </c>
       <c r="D14" s="16" t="n">
         <f aca="false">SUM(D9:D13)</f>
-        <v>46883548.8</v>
+        <v>47332195.2</v>
       </c>
       <c r="E14" s="16" t="n">
         <f aca="false">SUM(E9:E13)</f>
-        <v>49813770.6</v>
+        <v>50290457.4</v>
       </c>
       <c r="F14" s="16" t="n">
         <f aca="false">SUM(F9:F13)</f>
-        <v>49813770.6</v>
+        <v>50290457.4</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12410,7 +13066,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="29" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
@@ -12420,7 +13076,7 @@
     </row>
     <row r="17" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="B17" s="13" t="n">
         <f aca="false">人件費!$D$12</f>
@@ -12445,32 +13101,32 @@
     </row>
     <row r="18" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B18" s="13" t="n">
         <f aca="false">B11</f>
-        <v>775682.6</v>
+        <v>783105.4</v>
       </c>
       <c r="C18" s="13" t="n">
         <f aca="false">C11</f>
-        <v>1440553.4</v>
+        <v>1454338.6</v>
       </c>
       <c r="D18" s="13" t="n">
         <f aca="false">D11</f>
-        <v>1772988.8</v>
+        <v>1789955.2</v>
       </c>
       <c r="E18" s="13" t="n">
         <f aca="false">E11</f>
-        <v>1883800.6</v>
+        <v>1901827.4</v>
       </c>
       <c r="F18" s="13" t="n">
         <f aca="false">F11</f>
-        <v>1883800.6</v>
+        <v>1901827.4</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B19" s="10" t="n">
         <v>1200000</v>
@@ -12490,7 +13146,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B20" s="13" t="n">
         <f aca="false">前提条件!$B$21*12</f>
@@ -12515,7 +13171,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B21" s="13" t="n">
         <f aca="false">前提条件!$B$22</f>
@@ -12540,7 +13196,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B22" s="13" t="n">
         <f aca="false">前提条件!$B$23</f>
@@ -12565,7 +13221,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="B23" s="13" t="n">
         <f aca="false">前提条件!$B$24/前提条件!$B$25</f>
@@ -12590,27 +13246,27 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="29" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B24" s="16" t="n">
         <f aca="false">SUM(B17:B23)</f>
-        <v>54290182.6</v>
+        <v>54297605.4</v>
       </c>
       <c r="C24" s="16" t="n">
         <f aca="false">SUM(C17:C23)</f>
-        <v>54955053.4</v>
+        <v>54968838.6</v>
       </c>
       <c r="D24" s="16" t="n">
         <f aca="false">SUM(D17:D23)</f>
-        <v>57687488.8</v>
+        <v>57704455.2</v>
       </c>
       <c r="E24" s="16" t="n">
         <f aca="false">SUM(E17:E23)</f>
-        <v>57798300.6</v>
+        <v>57816327.4</v>
       </c>
       <c r="F24" s="16" t="n">
         <f aca="false">SUM(F17:F23)</f>
-        <v>57798300.6</v>
+        <v>57816327.4</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12623,52 +13279,52 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="29" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B26" s="16" t="n">
         <f aca="false">B14-B24</f>
-        <v>-33778630</v>
+        <v>-33589770</v>
       </c>
       <c r="C26" s="16" t="n">
         <f aca="false">C14-C24</f>
-        <v>-16862170</v>
+        <v>-16511430</v>
       </c>
       <c r="D26" s="16" t="n">
         <f aca="false">D14-D24</f>
-        <v>-10803940</v>
+        <v>-10372260</v>
       </c>
       <c r="E26" s="16" t="n">
         <f aca="false">E14-E24</f>
-        <v>-7984530.00000001</v>
+        <v>-7525869.99999999</v>
       </c>
       <c r="F26" s="16" t="n">
         <f aca="false">F14-F24</f>
-        <v>-7984530.00000001</v>
+        <v>-7525869.99999999</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B27" s="32" t="n">
+        <v>225</v>
+      </c>
+      <c r="B27" s="33" t="n">
         <f aca="false">IFERROR(B26/B14,0)</f>
-        <v>-1.6468100030614</v>
-      </c>
-      <c r="C27" s="32" t="n">
+        <v>-1.62208021027635</v>
+      </c>
+      <c r="C27" s="33" t="n">
         <f aca="false">IFERROR(C26/C14,0)</f>
-        <v>-0.442659323604787</v>
-      </c>
-      <c r="D27" s="32" t="n">
+        <v>-0.429343281335914</v>
+      </c>
+      <c r="D27" s="33" t="n">
         <f aca="false">IFERROR(D26/D14,0)</f>
-        <v>-0.230442026606996</v>
-      </c>
-      <c r="E27" s="32" t="n">
+        <v>-0.219137522698292</v>
+      </c>
+      <c r="E27" s="33" t="n">
         <f aca="false">IFERROR(E26/E14,0)</f>
-        <v>-0.160287605291217</v>
-      </c>
-      <c r="F27" s="32" t="n">
+        <v>-0.149648072200671</v>
+      </c>
+      <c r="F27" s="33" t="n">
         <f aca="false">IFERROR(F26/F14,0)</f>
-        <v>-0.160287605291217</v>
+        <v>-0.149648072200671</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12681,7 +13337,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="29" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
@@ -12691,32 +13347,32 @@
     </row>
     <row r="30" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="B30" s="13" t="n">
         <f aca="false">B26+B23</f>
-        <v>-31466130</v>
+        <v>-31277270</v>
       </c>
       <c r="C30" s="13" t="n">
         <f aca="false">C26+C23</f>
-        <v>-14549670</v>
+        <v>-14198930</v>
       </c>
       <c r="D30" s="13" t="n">
         <f aca="false">D26+D23</f>
-        <v>-8491440</v>
+        <v>-8059760</v>
       </c>
       <c r="E30" s="13" t="n">
         <f aca="false">E26+E23</f>
-        <v>-5672030.00000001</v>
+        <v>-5213369.99999999</v>
       </c>
       <c r="F30" s="13" t="n">
         <f aca="false">F26+F23</f>
-        <v>-5672030.00000001</v>
+        <v>-5213369.99999999</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B31" s="24" t="n">
         <v>0</v>
@@ -12736,52 +13392,52 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="B32" s="13" t="n">
         <f aca="false">B30-B31</f>
-        <v>-31466130</v>
+        <v>-31277270</v>
       </c>
       <c r="C32" s="13" t="n">
         <f aca="false">C30-C31</f>
-        <v>-18049670</v>
+        <v>-17698930</v>
       </c>
       <c r="D32" s="13" t="n">
         <f aca="false">D30-D31</f>
-        <v>-12491440</v>
+        <v>-12059760</v>
       </c>
       <c r="E32" s="13" t="n">
         <f aca="false">E30-E31</f>
-        <v>-9672030.00000001</v>
+        <v>-9213369.99999999</v>
       </c>
       <c r="F32" s="13" t="n">
         <f aca="false">F30-F31</f>
-        <v>-9672030.00000001</v>
+        <v>-9213369.99999999</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="29" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B33" s="16" t="n">
         <f aca="false">B32</f>
-        <v>-31466130</v>
+        <v>-31277270</v>
       </c>
       <c r="C33" s="16" t="n">
         <f aca="false">B33+C32</f>
-        <v>-49515800</v>
+        <v>-48976200</v>
       </c>
       <c r="D33" s="16" t="n">
         <f aca="false">C33+D32</f>
-        <v>-62007240</v>
+        <v>-61035960</v>
       </c>
       <c r="E33" s="16" t="n">
         <f aca="false">D33+E32</f>
-        <v>-71679270</v>
+        <v>-70249330</v>
       </c>
       <c r="F33" s="16" t="n">
         <f aca="false">E33+F32</f>
-        <v>-81351300</v>
+        <v>-79462700</v>
       </c>
     </row>
   </sheetData>

--- a/business-plan/収支計画_生活介護_広島市.xlsx
+++ b/business-plan/収支計画_生活介護_広島市.xlsx
@@ -18,6 +18,7 @@
     <sheet name="月次資金繰り(Year1)" sheetId="8" state="visible" r:id="rId10"/>
     <sheet name="収支計画5年" sheetId="9" state="visible" r:id="rId11"/>
     <sheet name="加算フル活用シナリオ" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="経営方針比較" sheetId="11" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="289">
   <si>
     <r>
       <rPr>
@@ -12528,6 +12529,1111 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">日以内はさらに上乗せがある制度になっているため、実際にはこれより上振れる可能性がある。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">経営方針比較 ― 理念優先</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採用中</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">とコスト圧縮</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不採用</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の試算</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6-3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">章・第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10-4-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">章で「理念の実現」を優先する経営方針を決定し、人員配置</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">総数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7.4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は法定最低ライン</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(6.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">へ圧縮しないことにした。本シートは、もし優先順位を逆にして人件費圧縮を選んでいた場合の試算を、参考として並べたものである。現時点の正式な採用シナリオは「理念優先」であり、下記のコスト圧縮シナリオは意思決定の材料としての比較であって、計画の変更ではない。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【前提】コスト圧縮シナリオ＝生活支援員等を法定最低ライン</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">総数</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6.0</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">まで削減し、人員配置体制加算Ⅲは取得しない</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">削減後は加算の配置要件を満たせないため</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">削減人数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">現行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7.4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名→法定最低</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">名。生活支援員等から削減する前提</t>
+  </si>
+  <si>
+    <t xml:space="preserve">年間削減人件費</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">項目</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">営業利益</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">①是正後ベースケース</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">加算Ⅲなし・圧縮なし</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">②理念優先</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採用中：加算Ⅲを</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Year3</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以降に段階導入</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">③コスト圧縮</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不採用：法定最低ラインへ削減、加算Ⅲなし</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※③は①に年間削減人件費を単純加算した試算</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">圧縮を全期間で適用した場合</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。人員を削減すると人員配置体制加算Ⅲの配置要件を満たせなくなるため②とは併用できない。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【③コスト圧縮シナリオの</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ヵ年資金試算】</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">簡易キャッシュフロー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(③</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">営業利益</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">減価償却費</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">単年キャッシュフロー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">融資返済控除後</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">累積キャッシュフロー</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">真の必要資金・ギャップ比較</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(②</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">理念優先＝現行の資金調達計画シートの数字／③コスト圧縮＝本シートの試算</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">②理念優先</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採用中</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">③コスト圧縮</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不採用</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※金額だけ見ればコスト圧縮の方が資金ギャップは小さい。ただし本シートは財務試算のみであり、以下は数字に表れない考慮事項である：①法定最低ライン</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(6.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ちょうどまで削減すると欠員</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">退職・急な休職</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">が即座に基準違反につながるバッファーがなくなる</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6-5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">章</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、②週複数回の地域外出等、理念に掲げた支援の質を維持できなくなる可能性が高い、③人員配置体制加算Ⅲ等の上位加算を将来的に狙う余地がなくなる。第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6-3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">章の経営方針決定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">理念優先</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は、これらを踏まえた上での判断である。</t>
     </r>
   </si>
 </sst>
@@ -13602,6 +14708,348 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+    </row>
+    <row r="2" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+    </row>
+    <row r="4" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="B5" s="18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="B6" s="9" t="n">
+        <f aca="false">加算フル活用シナリオ!$B$8</f>
+        <v>4140000</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="B7" s="26" t="n">
+        <f aca="false">B5*B6</f>
+        <v>5796000</v>
+      </c>
+      <c r="C7" s="14"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="B9" s="37" t="s">
+        <v>201</v>
+      </c>
+      <c r="C9" s="37" t="s">
+        <v>202</v>
+      </c>
+      <c r="D9" s="37" t="s">
+        <v>203</v>
+      </c>
+      <c r="E9" s="37" t="s">
+        <v>204</v>
+      </c>
+      <c r="F9" s="37" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="B10" s="13" t="n">
+        <f aca="false">収支計画5年!B$30-(収支計画5年!B$16-収支計画5年!B$27)</f>
+        <v>-33567615</v>
+      </c>
+      <c r="C10" s="13" t="n">
+        <f aca="false">収支計画5年!C$30-(収支計画5年!C$16-収支計画5年!C$27)</f>
+        <v>-16470285</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <f aca="false">収支計画5年!D$30-(収支計画5年!D$16-収支計画5年!D$27)</f>
+        <v>-10321620</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <f aca="false">収支計画5年!E$30-(収支計画5年!E$16-収支計画5年!E$27)</f>
+        <v>-7472064.99999999</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <f aca="false">収支計画5年!F$30-(収支計画5年!F$16-収支計画5年!F$27)</f>
+        <v>-7472064.99999999</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="30" t="s">
+        <v>278</v>
+      </c>
+      <c r="B11" s="16" t="n">
+        <f aca="false">収支計画5年!B$30</f>
+        <v>-33567615</v>
+      </c>
+      <c r="C11" s="16" t="n">
+        <f aca="false">収支計画5年!C$30</f>
+        <v>-16470285</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <f aca="false">収支計画5年!D$30</f>
+        <v>-8893420</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <f aca="false">収支計画5年!E$30</f>
+        <v>-5566477.49999999</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <f aca="false">収支計画5年!F$30</f>
+        <v>-5566477.49999999</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="B12" s="13" t="n">
+        <f aca="false">B10+$B$7</f>
+        <v>-27771615</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <f aca="false">C10+$B$7</f>
+        <v>-10674285</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <f aca="false">D10+$B$7</f>
+        <v>-4525620</v>
+      </c>
+      <c r="E12" s="13" t="n">
+        <f aca="false">E10+$B$7</f>
+        <v>-1676065</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <f aca="false">F10+$B$7</f>
+        <v>-1676065</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+    </row>
+    <row r="16" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="B17" s="13" t="n">
+        <f aca="false">B12+収支計画5年!B$26</f>
+        <v>-25459115</v>
+      </c>
+      <c r="C17" s="13" t="n">
+        <f aca="false">C12+収支計画5年!C$26</f>
+        <v>-8361785</v>
+      </c>
+      <c r="D17" s="13" t="n">
+        <f aca="false">D12+収支計画5年!D$26</f>
+        <v>-2213120</v>
+      </c>
+      <c r="E17" s="13" t="n">
+        <f aca="false">E12+収支計画5年!E$26</f>
+        <v>636435.000000005</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <f aca="false">F12+収支計画5年!F$26</f>
+        <v>636435.000000005</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="B18" s="13" t="n">
+        <f aca="false">B17-収支計画5年!B$35</f>
+        <v>-25459115</v>
+      </c>
+      <c r="C18" s="13" t="n">
+        <f aca="false">C17-収支計画5年!C$35</f>
+        <v>-11861785</v>
+      </c>
+      <c r="D18" s="13" t="n">
+        <f aca="false">D17-収支計画5年!D$35</f>
+        <v>-6213120</v>
+      </c>
+      <c r="E18" s="13" t="n">
+        <f aca="false">E17-収支計画5年!E$35</f>
+        <v>-3363565</v>
+      </c>
+      <c r="F18" s="13" t="n">
+        <f aca="false">F17-収支計画5年!F$35</f>
+        <v>-3363565</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="30" t="s">
+        <v>284</v>
+      </c>
+      <c r="B19" s="16" t="n">
+        <f aca="false">B18</f>
+        <v>-25459115</v>
+      </c>
+      <c r="C19" s="16" t="n">
+        <f aca="false">B19+C18</f>
+        <v>-37320900</v>
+      </c>
+      <c r="D19" s="16" t="n">
+        <f aca="false">C19+D18</f>
+        <v>-43534020</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <f aca="false">D19+E18</f>
+        <v>-46897585</v>
+      </c>
+      <c r="F19" s="16" t="n">
+        <f aca="false">E19+F18</f>
+        <v>-50261150</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="B23" s="13" t="n">
+        <f aca="false">資金調達計画!$B$20</f>
+        <v>104651775</v>
+      </c>
+      <c r="C23" s="13" t="n">
+        <f aca="false">資金調達計画!$B$18-F19</f>
+        <v>80911150</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="30" t="s">
+        <v>153</v>
+      </c>
+      <c r="B24" s="16" t="n">
+        <f aca="false">資金調達計画!$B$21</f>
+        <v>-64651775</v>
+      </c>
+      <c r="C24" s="16" t="n">
+        <f aca="false">資金調達計画!$B$13-C23</f>
+        <v>-40911150</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A26:F26"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">

--- a/business-plan/収支計画_生活介護_広島市.xlsx
+++ b/business-plan/収支計画_生活介護_広島市.xlsx
@@ -19,6 +19,7 @@
     <sheet name="収支計画5年" sheetId="9" state="visible" r:id="rId11"/>
     <sheet name="加算フル活用シナリオ" sheetId="10" state="visible" r:id="rId12"/>
     <sheet name="経営方針比較" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="成熟期シナリオ" sheetId="12" state="visible" r:id="rId14"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="311">
   <si>
     <r>
       <rPr>
@@ -13634,6 +13635,1861 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">は、これらを踏まえた上での判断である。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">成熟期シナリオ ― 「立ち上がり期」と「事業の潜在力」の切り分け</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「収支計画</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年」の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Year1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は、契約者数がゼロから積み上がる新規開業特有の立ち上がり期を含んでいる。本シートは、その立ち上がり期を終えて稼働率が定常化した「成熟期」だけを取り出した場合、事業の単年度収支がどうなるかを試算するもの。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ヵ年計画・資金計画</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">章</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を置き換えるものではなく、「事業モデルそのものに稼ぐ力があるか」を切り分けて確認するための補助シートである。青字セルは入力用。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">【前提】</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">成熟期稼働率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">想定・入力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">立ち上がり期を終え、紹介ルートが確立した後の定常的な稼働率の想定。現行計画の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Year5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">85%(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10-3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">章</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">90%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">はあくまで試算例であり、実際の水準は第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">章の営業活動の結果次第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未検証</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">想定利用者数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人。定員</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">成熟期稼働率</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">理念優先</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(7.4</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名＋加算Ⅲ、採用中の方針</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">法定最低ライン</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(6.0</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名、加算Ⅲなし・参考</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">送迎加算収入</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">処遇改善加算収入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">全額を人件費側に同額計上</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">入浴支援加算収入</t>
+  </si>
+  <si>
+    <t xml:space="preserve">食事提供体制加算収入</t>
+  </si>
+  <si>
+    <t xml:space="preserve">福祉専門職員配置等加算収入</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人員配置体制加算Ⅲ収入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">のみ。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は配置要件を満たせず対象外</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人件費</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">法定福利費込</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">処遇改善加算 相当額の賃金改善</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">損益中立</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">豊口氏 役員報酬</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">成熟期＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Year3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以降の水準</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人員配置体制加算Ⅲ対応 追加人件費</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">のみ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【参考】現行の</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ヵ年計画</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Year5(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">稼働率</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">85%</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。立ち上がり期を経た計画上の着地点、第</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10-3</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">章</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Year5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">営業利益</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">理念優先・加算Ⅲ導入後</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※本シートは「開業初日から成熟期稼働率に達している」という仮想の試算であり、実際には稼働率がゼロから積み上がるため、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Year1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">はこの水準に届かない</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10-3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">章の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ヵ年計画・第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">章の資金計画を参照</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">85%(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">現行計画の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Year5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">と同水準</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">にすると、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は現行の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Year5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">営業利益</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">下記参考行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">と完全に一致する。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">90%→95%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">と引き上げると、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">90%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時点で既に黒字化するのに対し、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">90%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ではなお赤字</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(▲224</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">95%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">でようやく黒字化する</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(+109</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。つまり「立ち上がり期を除けば必ず黒字」と単純には言えず、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の人員配置</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">理念優先</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を維持したまま黒字化するには、稼働率を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">85%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">からさらに引き上げる</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">概ね</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">93%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">前後が目安</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">必要がある。それでも言えるのは、①法定最低ライン</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(B)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">なら</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">90%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">程度の現実的な稼働率で黒字化する経済性があり、事業モデル自体が赤字体質とまでは言えないこと、②本計画の最大の課題は「稼働率をどこまで・どれだけ早く引き上げられるか」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">章、未着手</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">と「そこに至るまでの資金繰り」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">章</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に集約されること、の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点である。成熟期稼働率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(B5)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">自体も未検証の想定であり、佐伯区・西区の実際の需給</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">章</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で確定させる必要がある。</t>
     </r>
   </si>
 </sst>
@@ -15050,6 +16906,367 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C36"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+    </row>
+    <row r="2" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="B5" s="19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="B6" s="33" t="n">
+        <f aca="false">前提条件!$B$3*B5</f>
+        <v>18</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="37" t="s">
+        <v>296</v>
+      </c>
+      <c r="C8" s="37" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="B10" s="13" t="n">
+        <f aca="false">B6*前提条件!$B$5*前提条件!$B$9*前提条件!$B$21</f>
+        <v>45765900</v>
+      </c>
+      <c r="C10" s="13" t="n">
+        <f aca="false">B6*前提条件!$B$5*前提条件!$B$9*前提条件!$B$21</f>
+        <v>45765900</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="B11" s="13" t="n">
+        <f aca="false">B6*前提条件!$B$13*((前提条件!$B$10+前提条件!$B$12*前提条件!$B$11)*2)*前提条件!$B$9*前提条件!$B$21</f>
+        <v>3722040</v>
+      </c>
+      <c r="C11" s="13" t="n">
+        <f aca="false">B6*前提条件!$B$13*((前提条件!$B$10+前提条件!$B$12*前提条件!$B$11)*2)*前提条件!$B$9*前提条件!$B$21</f>
+        <v>3722040</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="B12" s="13" t="n">
+        <f aca="false">B10*前提条件!$B$14</f>
+        <v>3844335.6</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <f aca="false">C10*前提条件!$B$14</f>
+        <v>3844335.6</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="B13" s="13" t="n">
+        <f aca="false">B6*前提条件!$B$16*前提条件!$B$17*(前提条件!$B$21/5)*前提条件!$B$18*前提条件!$B$9</f>
+        <v>379800</v>
+      </c>
+      <c r="C13" s="13" t="n">
+        <f aca="false">B6*前提条件!$B$16*前提条件!$B$17*(前提条件!$B$21/5)*前提条件!$B$18*前提条件!$B$9</f>
+        <v>379800</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="B14" s="13" t="n">
+        <f aca="false">B6*前提条件!$B$19*前提条件!$B$20*前提条件!$B$9*前提条件!$B$21</f>
+        <v>427275</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <f aca="false">B6*前提条件!$B$19*前提条件!$B$20*前提条件!$B$9*前提条件!$B$21</f>
+        <v>427275</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="B15" s="13" t="n">
+        <f aca="false">B6*前提条件!$B$15*前提条件!$B$9*前提条件!$B$21</f>
+        <v>996975</v>
+      </c>
+      <c r="C15" s="13" t="n">
+        <f aca="false">B6*前提条件!$B$15*前提条件!$B$9*前提条件!$B$21</f>
+        <v>996975</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="B16" s="13" t="n">
+        <f aca="false">B6*加算フル活用シナリオ!$B$12*前提条件!$B$9*前提条件!$B$21</f>
+        <v>8592975</v>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="30" t="s">
+        <v>219</v>
+      </c>
+      <c r="B17" s="16" t="n">
+        <f aca="false">SUM(B10:B16)</f>
+        <v>63729300.6</v>
+      </c>
+      <c r="C17" s="16" t="n">
+        <f aca="false">SUM(C10:C16)</f>
+        <v>55136325.6</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="B20" s="13" t="n">
+        <f aca="false">人件費!$D$12</f>
+        <v>39652000</v>
+      </c>
+      <c r="C20" s="13" t="n">
+        <f aca="false">人件費!$D$12-経営方針比較!$B$7</f>
+        <v>33856000</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="B21" s="13" t="n">
+        <f aca="false">B12</f>
+        <v>3844335.6</v>
+      </c>
+      <c r="C21" s="13" t="n">
+        <f aca="false">C12</f>
+        <v>3844335.6</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="B22" s="13" t="n">
+        <f aca="false">3600000</f>
+        <v>3600000</v>
+      </c>
+      <c r="C22" s="13" t="n">
+        <f aca="false">3600000</f>
+        <v>3600000</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="B23" s="13" t="n">
+        <f aca="false">前提条件!$B$22*12</f>
+        <v>4800000</v>
+      </c>
+      <c r="C23" s="13" t="n">
+        <f aca="false">前提条件!$B$22*12</f>
+        <v>4800000</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="B24" s="13" t="n">
+        <f aca="false">前提条件!$B$23</f>
+        <v>900000</v>
+      </c>
+      <c r="C24" s="13" t="n">
+        <f aca="false">前提条件!$B$23</f>
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="B25" s="13" t="n">
+        <f aca="false">前提条件!$B$24</f>
+        <v>4650000</v>
+      </c>
+      <c r="C25" s="13" t="n">
+        <f aca="false">前提条件!$B$24</f>
+        <v>4650000</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="B26" s="13" t="n">
+        <f aca="false">前提条件!$B$25/前提条件!$B$26</f>
+        <v>2312500</v>
+      </c>
+      <c r="C26" s="13" t="n">
+        <f aca="false">前提条件!$B$25/前提条件!$B$26</f>
+        <v>2312500</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="B27" s="13" t="n">
+        <f aca="false">加算フル活用シナリオ!$C$12*加算フル活用シナリオ!$B$8</f>
+        <v>6210000</v>
+      </c>
+      <c r="C27" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="30" t="s">
+        <v>229</v>
+      </c>
+      <c r="B28" s="16" t="n">
+        <f aca="false">SUM(B19:B27)</f>
+        <v>65968835.6</v>
+      </c>
+      <c r="C28" s="16" t="n">
+        <f aca="false">SUM(C19:C27)</f>
+        <v>53962835.6</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="30" t="s">
+        <v>230</v>
+      </c>
+      <c r="B30" s="16" t="n">
+        <f aca="false">B17-B28</f>
+        <v>-2239535</v>
+      </c>
+      <c r="C30" s="16" t="n">
+        <f aca="false">C17-C28</f>
+        <v>1173490</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="B31" s="34" t="n">
+        <f aca="false">IFERROR(B30/B17,0)</f>
+        <v>-0.0351413710634697</v>
+      </c>
+      <c r="C31" s="34" t="n">
+        <f aca="false">IFERROR(C30/C17,0)</f>
+        <v>0.0212834277081388</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="B34" s="13" t="n">
+        <f aca="false">収支計画5年!$F$30</f>
+        <v>-5566477.49999999</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A36:C36"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">

--- a/business-plan/収支計画_生活介護_広島市.xlsx
+++ b/business-plan/収支計画_生活介護_広島市.xlsx
@@ -20,7 +20,11 @@
     <sheet name="加算フル活用シナリオ" sheetId="10" state="visible" r:id="rId12"/>
     <sheet name="配置比率シナリオ比較" sheetId="11" state="visible" r:id="rId13"/>
     <sheet name="満床シナリオ" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="費用内訳レビュー" sheetId="13" state="visible" r:id="rId15"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="false" localSheetId="12" name="_xlnm.Print_Area" vbProcedure="false">費用内訳レビュー!$A$1:$G$63</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -31,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="326">
   <si>
     <r>
       <rPr>
@@ -14621,6 +14625,1162 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">を圧縮する、のいずれか・組み合わせが必要になる。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">収支・費用 一覧表</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">検討用</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) ― </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">明日の打ち合わせで費用を見直すためのレビューシート</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">下表はすべて「収支計画</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年」「人件費」「前提条件」シートの数式参照であり、独自の数値は持たない</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">数値を変えたい場合は参照元のシートを編集すること</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">G</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">列「見直し案・メモ」は空欄。打ち合わせ中に検討結果を書き込むための欄。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">】収入内訳</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年次</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">見直し案・メモ</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">処遇改善加算収入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">全額を人件費側に同額計上・損益中立</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">】経費内訳</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年次サマリー。人件費の内訳は【</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">】、その他経費の内訳は【</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">】参照</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人件費</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">法定福利費込。内訳は【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">豊口氏 役員報酬</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">その他経費</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">内訳は【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">営業利益</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">収入合計－経費合計</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">】人件費の内訳</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">職種別・年次。「人件費」シートより参照</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">法定福利費等</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">概算</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15%)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">参考</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">職種別 人数</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">常勤換算</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">合計人数</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">常勤換算</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">】その他経費の内訳</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年間・全年共通。「前提条件」シートより参照</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">その他経費 合計</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年間</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">⚠ 費用を見直す際の視点：①生活支援員等の人数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は配置比率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.5:1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を維持する前提の自動算出値であり、配置比率を緩める</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(3:1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">側に近づける</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">と人数・人件費が大きく下がる一方、理念とのトレードオフが生じる</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10-4-2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">章「配置比率シナリオ比較」参照</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。②地代家賃・その他経費</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は居抜き物件の活用度合いや契約内容次第で圧縮余地がある。③役員報酬</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">豊口氏</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Year3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以降月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円を想定しているが、時期・金額は調整可能な項目である。④送迎車両・什器等の初期投資</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">別紙「初期投資」シート</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は減価償却費に影響するため、購入かリースかの見直しも選択肢。</t>
     </r>
   </si>
 </sst>
@@ -14808,7 +15968,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -14998,6 +16158,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -16084,6 +17248,1237 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:G63"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="26"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+    </row>
+    <row r="2" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15" t="s">
+        <v>311</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="E5" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="F5" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="B6" s="13" t="n">
+        <f aca="false">収支計画5年!B$9</f>
+        <v>10170200</v>
+      </c>
+      <c r="C6" s="13" t="n">
+        <f aca="false">収支計画5年!C$9</f>
+        <v>17797850</v>
+      </c>
+      <c r="D6" s="13" t="n">
+        <f aca="false">収支計画5年!D$9</f>
+        <v>26696775</v>
+      </c>
+      <c r="E6" s="13" t="n">
+        <f aca="false">収支計画5年!E$9</f>
+        <v>36866975</v>
+      </c>
+      <c r="F6" s="13" t="n">
+        <f aca="false">収支計画5年!F$9</f>
+        <v>47037175</v>
+      </c>
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="B7" s="13" t="n">
+        <f aca="false">収支計画5年!B$10</f>
+        <v>827120</v>
+      </c>
+      <c r="C7" s="13" t="n">
+        <f aca="false">収支計画5年!C$10</f>
+        <v>1447460</v>
+      </c>
+      <c r="D7" s="13" t="n">
+        <f aca="false">収支計画5年!D$10</f>
+        <v>2171190</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <f aca="false">収支計画5年!E$10</f>
+        <v>2998310</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <f aca="false">収支計画5年!F$10</f>
+        <v>3825430</v>
+      </c>
+      <c r="G7" s="14"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="B8" s="13" t="n">
+        <f aca="false">収支計画5年!B$11</f>
+        <v>854296.8</v>
+      </c>
+      <c r="C8" s="13" t="n">
+        <f aca="false">収支計画5年!C$11</f>
+        <v>1495019.4</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <f aca="false">収支計画5年!D$11</f>
+        <v>2242529.1</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <f aca="false">収支計画5年!E$11</f>
+        <v>3096825.9</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <f aca="false">収支計画5年!F$11</f>
+        <v>3951122.7</v>
+      </c>
+      <c r="G8" s="14"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="B9" s="13" t="n">
+        <f aca="false">収支計画5年!B$12</f>
+        <v>84400</v>
+      </c>
+      <c r="C9" s="13" t="n">
+        <f aca="false">収支計画5年!C$12</f>
+        <v>147700</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <f aca="false">収支計画5年!D$12</f>
+        <v>221550</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <f aca="false">収支計画5年!E$12</f>
+        <v>305950</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <f aca="false">収支計画5年!F$12</f>
+        <v>390350</v>
+      </c>
+      <c r="G9" s="14"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="B10" s="13" t="n">
+        <f aca="false">収支計画5年!B$13</f>
+        <v>94950</v>
+      </c>
+      <c r="C10" s="13" t="n">
+        <f aca="false">収支計画5年!C$13</f>
+        <v>166162.5</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <f aca="false">収支計画5年!D$13</f>
+        <v>249243.75</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <f aca="false">収支計画5年!E$13</f>
+        <v>344193.75</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <f aca="false">収支計画5年!F$13</f>
+        <v>439143.75</v>
+      </c>
+      <c r="G10" s="14"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="B11" s="13" t="n">
+        <f aca="false">収支計画5年!B$14</f>
+        <v>221550</v>
+      </c>
+      <c r="C11" s="13" t="n">
+        <f aca="false">収支計画5年!C$14</f>
+        <v>387712.5</v>
+      </c>
+      <c r="D11" s="13" t="n">
+        <f aca="false">収支計画5年!D$14</f>
+        <v>581568.75</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <f aca="false">収支計画5年!E$14</f>
+        <v>803118.75</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <f aca="false">収支計画5年!F$14</f>
+        <v>1024668.75</v>
+      </c>
+      <c r="G11" s="14"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="B12" s="13" t="n">
+        <f aca="false">収支計画5年!B$15</f>
+        <v>3386550</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <f aca="false">収支計画5年!C$15</f>
+        <v>5926462.5</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <f aca="false">収支計画5年!D$15</f>
+        <v>8889693.75</v>
+      </c>
+      <c r="E12" s="13" t="n">
+        <f aca="false">収支計画5年!E$15</f>
+        <v>12276243.75</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <f aca="false">収支計画5年!F$15</f>
+        <v>15662793.75</v>
+      </c>
+      <c r="G12" s="14"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="35" t="s">
+        <v>237</v>
+      </c>
+      <c r="B13" s="16" t="n">
+        <f aca="false">収支計画5年!B$16</f>
+        <v>15639066.8</v>
+      </c>
+      <c r="C13" s="16" t="n">
+        <f aca="false">収支計画5年!C$16</f>
+        <v>27368366.9</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <f aca="false">収支計画5年!D$16</f>
+        <v>41052550.35</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <f aca="false">収支計画5年!E$16</f>
+        <v>56691617.15</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <f aca="false">収支計画5年!F$16</f>
+        <v>72330683.95</v>
+      </c>
+      <c r="G13" s="14"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="15" t="s">
+        <v>314</v>
+      </c>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="D16" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="E16" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="F16" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="B17" s="13" t="n">
+        <f aca="false">収支計画5年!B$19</f>
+        <v>19320000</v>
+      </c>
+      <c r="C17" s="13" t="n">
+        <f aca="false">収支計画5年!C$19</f>
+        <v>29440000</v>
+      </c>
+      <c r="D17" s="13" t="n">
+        <f aca="false">収支計画5年!D$19</f>
+        <v>39652000</v>
+      </c>
+      <c r="E17" s="13" t="n">
+        <f aca="false">収支計画5年!E$19</f>
+        <v>52072000</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <f aca="false">収支計画5年!F$19</f>
+        <v>60352000</v>
+      </c>
+      <c r="G17" s="14"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="B18" s="13" t="n">
+        <f aca="false">収支計画5年!B$20</f>
+        <v>854296.8</v>
+      </c>
+      <c r="C18" s="13" t="n">
+        <f aca="false">収支計画5年!C$20</f>
+        <v>1495019.4</v>
+      </c>
+      <c r="D18" s="13" t="n">
+        <f aca="false">収支計画5年!D$20</f>
+        <v>2242529.1</v>
+      </c>
+      <c r="E18" s="13" t="n">
+        <f aca="false">収支計画5年!E$20</f>
+        <v>3096825.9</v>
+      </c>
+      <c r="F18" s="13" t="n">
+        <f aca="false">収支計画5年!F$20</f>
+        <v>3951122.7</v>
+      </c>
+      <c r="G18" s="14"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="B19" s="13" t="n">
+        <f aca="false">収支計画5年!B$21</f>
+        <v>1200000</v>
+      </c>
+      <c r="C19" s="13" t="n">
+        <f aca="false">収支計画5年!C$21</f>
+        <v>1200000</v>
+      </c>
+      <c r="D19" s="13" t="n">
+        <f aca="false">収支計画5年!D$21</f>
+        <v>3600000</v>
+      </c>
+      <c r="E19" s="13" t="n">
+        <f aca="false">収支計画5年!E$21</f>
+        <v>3600000</v>
+      </c>
+      <c r="F19" s="13" t="n">
+        <f aca="false">収支計画5年!F$21</f>
+        <v>3600000</v>
+      </c>
+      <c r="G19" s="14"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="B20" s="13" t="n">
+        <f aca="false">収支計画5年!B$22</f>
+        <v>4800000</v>
+      </c>
+      <c r="C20" s="13" t="n">
+        <f aca="false">収支計画5年!C$22</f>
+        <v>4800000</v>
+      </c>
+      <c r="D20" s="13" t="n">
+        <f aca="false">収支計画5年!D$22</f>
+        <v>4800000</v>
+      </c>
+      <c r="E20" s="13" t="n">
+        <f aca="false">収支計画5年!E$22</f>
+        <v>4800000</v>
+      </c>
+      <c r="F20" s="13" t="n">
+        <f aca="false">収支計画5年!F$22</f>
+        <v>4800000</v>
+      </c>
+      <c r="G20" s="14"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="B21" s="13" t="n">
+        <f aca="false">収支計画5年!B$23</f>
+        <v>900000</v>
+      </c>
+      <c r="C21" s="13" t="n">
+        <f aca="false">収支計画5年!C$23</f>
+        <v>900000</v>
+      </c>
+      <c r="D21" s="13" t="n">
+        <f aca="false">収支計画5年!D$23</f>
+        <v>900000</v>
+      </c>
+      <c r="E21" s="13" t="n">
+        <f aca="false">収支計画5年!E$23</f>
+        <v>900000</v>
+      </c>
+      <c r="F21" s="13" t="n">
+        <f aca="false">収支計画5年!F$23</f>
+        <v>900000</v>
+      </c>
+      <c r="G21" s="14"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="B22" s="13" t="n">
+        <f aca="false">収支計画5年!B$24</f>
+        <v>4650000</v>
+      </c>
+      <c r="C22" s="13" t="n">
+        <f aca="false">収支計画5年!C$24</f>
+        <v>4650000</v>
+      </c>
+      <c r="D22" s="13" t="n">
+        <f aca="false">収支計画5年!D$24</f>
+        <v>4650000</v>
+      </c>
+      <c r="E22" s="13" t="n">
+        <f aca="false">収支計画5年!E$24</f>
+        <v>4650000</v>
+      </c>
+      <c r="F22" s="13" t="n">
+        <f aca="false">収支計画5年!F$24</f>
+        <v>4650000</v>
+      </c>
+      <c r="G22" s="14"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="B23" s="13" t="n">
+        <f aca="false">収支計画5年!B$25</f>
+        <v>2312500</v>
+      </c>
+      <c r="C23" s="13" t="n">
+        <f aca="false">収支計画5年!C$25</f>
+        <v>2312500</v>
+      </c>
+      <c r="D23" s="13" t="n">
+        <f aca="false">収支計画5年!D$25</f>
+        <v>2312500</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <f aca="false">収支計画5年!E$25</f>
+        <v>2312500</v>
+      </c>
+      <c r="F23" s="13" t="n">
+        <f aca="false">収支計画5年!F$25</f>
+        <v>2312500</v>
+      </c>
+      <c r="G23" s="14"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="35" t="s">
+        <v>246</v>
+      </c>
+      <c r="B24" s="16" t="n">
+        <f aca="false">収支計画5年!B$26</f>
+        <v>34036796.8</v>
+      </c>
+      <c r="C24" s="16" t="n">
+        <f aca="false">収支計画5年!C$26</f>
+        <v>44797519.4</v>
+      </c>
+      <c r="D24" s="16" t="n">
+        <f aca="false">収支計画5年!D$26</f>
+        <v>58157029.1</v>
+      </c>
+      <c r="E24" s="16" t="n">
+        <f aca="false">収支計画5年!E$26</f>
+        <v>71431325.9</v>
+      </c>
+      <c r="F24" s="16" t="n">
+        <f aca="false">収支計画5年!F$26</f>
+        <v>80565622.7</v>
+      </c>
+      <c r="G24" s="14"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="35" t="s">
+        <v>318</v>
+      </c>
+      <c r="B26" s="16" t="n">
+        <f aca="false">収支計画5年!B$28</f>
+        <v>-18397730</v>
+      </c>
+      <c r="C26" s="16" t="n">
+        <f aca="false">収支計画5年!C$28</f>
+        <v>-17429152.5</v>
+      </c>
+      <c r="D26" s="16" t="n">
+        <f aca="false">収支計画5年!D$28</f>
+        <v>-17104478.75</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <f aca="false">収支計画5年!E$28</f>
+        <v>-14739708.75</v>
+      </c>
+      <c r="F26" s="16" t="n">
+        <f aca="false">収支計画5年!F$28</f>
+        <v>-8234938.75</v>
+      </c>
+      <c r="G26" s="14"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="B27" s="41" t="n">
+        <f aca="false">収支計画5年!B$29</f>
+        <v>-1.17639564017976</v>
+      </c>
+      <c r="C27" s="41" t="n">
+        <f aca="false">収支計画5年!C$29</f>
+        <v>-0.636835678346595</v>
+      </c>
+      <c r="D27" s="41" t="n">
+        <f aca="false">収支計画5年!D$29</f>
+        <v>-0.416648383697799</v>
+      </c>
+      <c r="E27" s="41" t="n">
+        <f aca="false">収支計画5年!E$29</f>
+        <v>-0.259998029532308</v>
+      </c>
+      <c r="F27" s="41" t="n">
+        <f aca="false">収支計画5年!F$29</f>
+        <v>-0.11385124957055</v>
+      </c>
+      <c r="G27" s="14"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="C30" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="D30" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="E30" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="F30" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="B31" s="13" t="n">
+        <f aca="false">人件費!B$15</f>
+        <v>4800000</v>
+      </c>
+      <c r="C31" s="13" t="n">
+        <f aca="false">人件費!C$15</f>
+        <v>4800000</v>
+      </c>
+      <c r="D31" s="13" t="n">
+        <f aca="false">人件費!D$15</f>
+        <v>4800000</v>
+      </c>
+      <c r="E31" s="13" t="n">
+        <f aca="false">人件費!E$15</f>
+        <v>4800000</v>
+      </c>
+      <c r="F31" s="13" t="n">
+        <f aca="false">人件費!F$15</f>
+        <v>4800000</v>
+      </c>
+      <c r="G31" s="14"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="B32" s="13" t="n">
+        <f aca="false">人件費!B$16</f>
+        <v>4200000</v>
+      </c>
+      <c r="C32" s="13" t="n">
+        <f aca="false">人件費!C$16</f>
+        <v>4200000</v>
+      </c>
+      <c r="D32" s="13" t="n">
+        <f aca="false">人件費!D$16</f>
+        <v>4200000</v>
+      </c>
+      <c r="E32" s="13" t="n">
+        <f aca="false">人件費!E$16</f>
+        <v>4200000</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <f aca="false">人件費!F$16</f>
+        <v>4200000</v>
+      </c>
+      <c r="G32" s="14"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="B33" s="13" t="n">
+        <f aca="false">人件費!B$17</f>
+        <v>0</v>
+      </c>
+      <c r="C33" s="13" t="n">
+        <f aca="false">人件費!C$17</f>
+        <v>0</v>
+      </c>
+      <c r="D33" s="13" t="n">
+        <f aca="false">人件費!D$17</f>
+        <v>1680000</v>
+      </c>
+      <c r="E33" s="13" t="n">
+        <f aca="false">人件費!E$17</f>
+        <v>1680000</v>
+      </c>
+      <c r="F33" s="13" t="n">
+        <f aca="false">人件費!F$17</f>
+        <v>1680000</v>
+      </c>
+      <c r="G33" s="14"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="B34" s="13" t="n">
+        <f aca="false">人件費!B$18</f>
+        <v>0</v>
+      </c>
+      <c r="C34" s="13" t="n">
+        <f aca="false">人件費!C$18</f>
+        <v>1600000</v>
+      </c>
+      <c r="D34" s="13" t="n">
+        <f aca="false">人件費!D$18</f>
+        <v>1600000</v>
+      </c>
+      <c r="E34" s="13" t="n">
+        <f aca="false">人件費!E$18</f>
+        <v>1600000</v>
+      </c>
+      <c r="F34" s="13" t="n">
+        <f aca="false">人件費!F$18</f>
+        <v>1600000</v>
+      </c>
+      <c r="G34" s="14"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B35" s="13" t="n">
+        <f aca="false">人件費!B$19</f>
+        <v>7200000</v>
+      </c>
+      <c r="C35" s="13" t="n">
+        <f aca="false">人件費!C$19</f>
+        <v>14400000</v>
+      </c>
+      <c r="D35" s="13" t="n">
+        <f aca="false">人件費!D$19</f>
+        <v>21600000</v>
+      </c>
+      <c r="E35" s="13" t="n">
+        <f aca="false">人件費!E$19</f>
+        <v>32400000</v>
+      </c>
+      <c r="F35" s="13" t="n">
+        <f aca="false">人件費!F$19</f>
+        <v>39600000</v>
+      </c>
+      <c r="G35" s="14"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="B36" s="13" t="n">
+        <f aca="false">人件費!B$20</f>
+        <v>600000</v>
+      </c>
+      <c r="C36" s="13" t="n">
+        <f aca="false">人件費!C$20</f>
+        <v>600000</v>
+      </c>
+      <c r="D36" s="13" t="n">
+        <f aca="false">人件費!D$20</f>
+        <v>600000</v>
+      </c>
+      <c r="E36" s="13" t="n">
+        <f aca="false">人件費!E$20</f>
+        <v>600000</v>
+      </c>
+      <c r="F36" s="13" t="n">
+        <f aca="false">人件費!F$20</f>
+        <v>600000</v>
+      </c>
+      <c r="G36" s="14"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="35" t="s">
+        <v>152</v>
+      </c>
+      <c r="B37" s="16" t="n">
+        <f aca="false">人件費!B$21</f>
+        <v>16800000</v>
+      </c>
+      <c r="C37" s="16" t="n">
+        <f aca="false">人件費!C$21</f>
+        <v>25600000</v>
+      </c>
+      <c r="D37" s="16" t="n">
+        <f aca="false">人件費!D$21</f>
+        <v>34480000</v>
+      </c>
+      <c r="E37" s="16" t="n">
+        <f aca="false">人件費!E$21</f>
+        <v>45280000</v>
+      </c>
+      <c r="F37" s="16" t="n">
+        <f aca="false">人件費!F$21</f>
+        <v>52480000</v>
+      </c>
+      <c r="G37" s="14"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="B38" s="13" t="n">
+        <f aca="false">人件費!B$22</f>
+        <v>2520000</v>
+      </c>
+      <c r="C38" s="13" t="n">
+        <f aca="false">人件費!C$22</f>
+        <v>3840000</v>
+      </c>
+      <c r="D38" s="13" t="n">
+        <f aca="false">人件費!D$22</f>
+        <v>5172000</v>
+      </c>
+      <c r="E38" s="13" t="n">
+        <f aca="false">人件費!E$22</f>
+        <v>6792000</v>
+      </c>
+      <c r="F38" s="13" t="n">
+        <f aca="false">人件費!F$22</f>
+        <v>7872000</v>
+      </c>
+      <c r="G38" s="14"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="35" t="s">
+        <v>154</v>
+      </c>
+      <c r="B39" s="16" t="n">
+        <f aca="false">人件費!B$23</f>
+        <v>19320000</v>
+      </c>
+      <c r="C39" s="16" t="n">
+        <f aca="false">人件費!C$23</f>
+        <v>29440000</v>
+      </c>
+      <c r="D39" s="16" t="n">
+        <f aca="false">人件費!D$23</f>
+        <v>39652000</v>
+      </c>
+      <c r="E39" s="16" t="n">
+        <f aca="false">人件費!E$23</f>
+        <v>52072000</v>
+      </c>
+      <c r="F39" s="16" t="n">
+        <f aca="false">人件費!F$23</f>
+        <v>60352000</v>
+      </c>
+      <c r="G39" s="14"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="48" t="s">
+        <v>321</v>
+      </c>
+      <c r="B41" s="17"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="17"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B42" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="C42" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="D42" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="E42" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="F42" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="B43" s="34" t="n">
+        <f aca="false">人件費!B$5</f>
+        <v>1</v>
+      </c>
+      <c r="C43" s="34" t="n">
+        <f aca="false">人件費!C$5</f>
+        <v>1</v>
+      </c>
+      <c r="D43" s="34" t="n">
+        <f aca="false">人件費!D$5</f>
+        <v>1</v>
+      </c>
+      <c r="E43" s="34" t="n">
+        <f aca="false">人件費!E$5</f>
+        <v>1</v>
+      </c>
+      <c r="F43" s="34" t="n">
+        <f aca="false">人件費!F$5</f>
+        <v>1</v>
+      </c>
+      <c r="G43" s="14"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="B44" s="34" t="n">
+        <f aca="false">人件費!B$6</f>
+        <v>1</v>
+      </c>
+      <c r="C44" s="34" t="n">
+        <f aca="false">人件費!C$6</f>
+        <v>1</v>
+      </c>
+      <c r="D44" s="34" t="n">
+        <f aca="false">人件費!D$6</f>
+        <v>1</v>
+      </c>
+      <c r="E44" s="34" t="n">
+        <f aca="false">人件費!E$6</f>
+        <v>1</v>
+      </c>
+      <c r="F44" s="34" t="n">
+        <f aca="false">人件費!F$6</f>
+        <v>1</v>
+      </c>
+      <c r="G44" s="14"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="B45" s="34" t="n">
+        <f aca="false">人件費!B$7</f>
+        <v>0</v>
+      </c>
+      <c r="C45" s="34" t="n">
+        <f aca="false">人件費!C$7</f>
+        <v>0</v>
+      </c>
+      <c r="D45" s="34" t="n">
+        <f aca="false">人件費!D$7</f>
+        <v>0.4</v>
+      </c>
+      <c r="E45" s="34" t="n">
+        <f aca="false">人件費!E$7</f>
+        <v>0.4</v>
+      </c>
+      <c r="F45" s="34" t="n">
+        <f aca="false">人件費!F$7</f>
+        <v>0.4</v>
+      </c>
+      <c r="G45" s="14"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="B46" s="34" t="n">
+        <f aca="false">人件費!B$8</f>
+        <v>0</v>
+      </c>
+      <c r="C46" s="34" t="n">
+        <f aca="false">人件費!C$8</f>
+        <v>0.5</v>
+      </c>
+      <c r="D46" s="34" t="n">
+        <f aca="false">人件費!D$8</f>
+        <v>0.5</v>
+      </c>
+      <c r="E46" s="34" t="n">
+        <f aca="false">人件費!E$8</f>
+        <v>0.5</v>
+      </c>
+      <c r="F46" s="34" t="n">
+        <f aca="false">人件費!F$8</f>
+        <v>0.5</v>
+      </c>
+      <c r="G46" s="14"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B47" s="34" t="n">
+        <f aca="false">人件費!B$9</f>
+        <v>2</v>
+      </c>
+      <c r="C47" s="34" t="n">
+        <f aca="false">人件費!C$9</f>
+        <v>4</v>
+      </c>
+      <c r="D47" s="34" t="n">
+        <f aca="false">人件費!D$9</f>
+        <v>6</v>
+      </c>
+      <c r="E47" s="34" t="n">
+        <f aca="false">人件費!E$9</f>
+        <v>9</v>
+      </c>
+      <c r="F47" s="34" t="n">
+        <f aca="false">人件費!F$9</f>
+        <v>11</v>
+      </c>
+      <c r="G47" s="14"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="35" t="s">
+        <v>322</v>
+      </c>
+      <c r="B48" s="36" t="n">
+        <f aca="false">人件費!B$11</f>
+        <v>4</v>
+      </c>
+      <c r="C48" s="36" t="n">
+        <f aca="false">人件費!C$11</f>
+        <v>6.5</v>
+      </c>
+      <c r="D48" s="36" t="n">
+        <f aca="false">人件費!D$11</f>
+        <v>8.9</v>
+      </c>
+      <c r="E48" s="36" t="n">
+        <f aca="false">人件費!E$11</f>
+        <v>11.9</v>
+      </c>
+      <c r="F48" s="36" t="n">
+        <f aca="false">人件費!F$11</f>
+        <v>13.9</v>
+      </c>
+      <c r="G48" s="14"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="B50" s="17"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="17"/>
+      <c r="F50" s="17"/>
+      <c r="G50" s="17"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="9" t="str">
+        <f aca="false">前提条件!$A$38</f>
+        <v>水道光熱費・消耗品費</v>
+      </c>
+      <c r="B52" s="13" t="n">
+        <f aca="false">前提条件!$B$38</f>
+        <v>900000</v>
+      </c>
+      <c r="C52" s="14"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="14"/>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="9" t="str">
+        <f aca="false">前提条件!$A$39</f>
+        <v>給食材料費(外部委託費)</v>
+      </c>
+      <c r="B53" s="13" t="n">
+        <f aca="false">前提条件!$B$39</f>
+        <v>1500000</v>
+      </c>
+      <c r="C53" s="14"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="14"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="14"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="9" t="str">
+        <f aca="false">前提条件!$A$40</f>
+        <v>嘱託医費用</v>
+      </c>
+      <c r="B54" s="13" t="n">
+        <f aca="false">前提条件!$B$40</f>
+        <v>400000</v>
+      </c>
+      <c r="C54" s="14"/>
+      <c r="D54" s="14"/>
+      <c r="E54" s="14"/>
+      <c r="F54" s="14"/>
+      <c r="G54" s="14"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="9" t="str">
+        <f aca="false">前提条件!$A$41</f>
+        <v>税理士顧問料・決算料</v>
+      </c>
+      <c r="B55" s="13" t="n">
+        <f aca="false">前提条件!$B$41</f>
+        <v>600000</v>
+      </c>
+      <c r="C55" s="14"/>
+      <c r="D55" s="14"/>
+      <c r="E55" s="14"/>
+      <c r="F55" s="14"/>
+      <c r="G55" s="14"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="9" t="str">
+        <f aca="false">前提条件!$A$42</f>
+        <v>社会保険労務士費用</v>
+      </c>
+      <c r="B56" s="13" t="n">
+        <f aca="false">前提条件!$B$42</f>
+        <v>200000</v>
+      </c>
+      <c r="C56" s="14"/>
+      <c r="D56" s="14"/>
+      <c r="E56" s="14"/>
+      <c r="F56" s="14"/>
+      <c r="G56" s="14"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="9" t="str">
+        <f aca="false">前提条件!$A$43</f>
+        <v>記録・請求システム利用料</v>
+      </c>
+      <c r="B57" s="13" t="n">
+        <f aca="false">前提条件!$B$43</f>
+        <v>300000</v>
+      </c>
+      <c r="C57" s="14"/>
+      <c r="D57" s="14"/>
+      <c r="E57" s="14"/>
+      <c r="F57" s="14"/>
+      <c r="G57" s="14"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="9" t="str">
+        <f aca="false">前提条件!$A$44</f>
+        <v>損害賠償責任保険・傷害保険</v>
+      </c>
+      <c r="B58" s="13" t="n">
+        <f aca="false">前提条件!$B$44</f>
+        <v>250000</v>
+      </c>
+      <c r="C58" s="14"/>
+      <c r="D58" s="14"/>
+      <c r="E58" s="14"/>
+      <c r="F58" s="14"/>
+      <c r="G58" s="14"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="9" t="str">
+        <f aca="false">前提条件!$A$45</f>
+        <v>職員健康診断</v>
+      </c>
+      <c r="B59" s="13" t="n">
+        <f aca="false">前提条件!$B$45</f>
+        <v>100000</v>
+      </c>
+      <c r="C59" s="14"/>
+      <c r="D59" s="14"/>
+      <c r="E59" s="14"/>
+      <c r="F59" s="14"/>
+      <c r="G59" s="14"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="9" t="str">
+        <f aca="false">前提条件!$A$46</f>
+        <v>研修費・広告費・虐待防止/BCP等体制整備費</v>
+      </c>
+      <c r="B60" s="13" t="n">
+        <f aca="false">前提条件!$B$46</f>
+        <v>400000</v>
+      </c>
+      <c r="C60" s="14"/>
+      <c r="D60" s="14"/>
+      <c r="E60" s="14"/>
+      <c r="F60" s="14"/>
+      <c r="G60" s="14"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="35" t="s">
+        <v>324</v>
+      </c>
+      <c r="B61" s="16" t="n">
+        <f aca="false">前提条件!$B$24</f>
+        <v>4650000</v>
+      </c>
+      <c r="C61" s="14"/>
+      <c r="D61" s="14"/>
+      <c r="E61" s="14"/>
+      <c r="F61" s="14"/>
+      <c r="G61" s="14"/>
+    </row>
+    <row r="63" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="B63" s="7"/>
+      <c r="C63" s="7"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="7"/>
+      <c r="G63" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A63:G63"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
